--- a/multilevel_regions.xlsx
+++ b/multilevel_regions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://princetonu-my.sharepoint.com/personal/lz8990_princeton_edu/Documents/Princeton/RA/admixture/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lz8990/Documents/GitHub/estimating_admixture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="13_ncr:1_{EC08447A-B797-0D40-BFDA-304B9BA53F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB9F59A4-DECB-2B4A-BF70-F231DE458EA3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B32C44B1-A653-0C4A-AB70-28D04889C33E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="19200" windowHeight="18620" xr2:uid="{94F556B0-DCF9-204A-A4B8-D01DCFFD1957}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="19200" windowHeight="16620" xr2:uid="{94F556B0-DCF9-204A-A4B8-D01DCFFD1957}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
